--- a/Extracted_data_analysis/polar/Output-Transformed_data/eco_reg_tot.xlsx
+++ b/Extracted_data_analysis/polar/Output-Transformed_data/eco_reg_tot.xlsx
@@ -3828,7 +3828,7 @@
         <v>20054</v>
       </c>
       <c r="K77">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -5853,7 +5853,7 @@
         <v>25055</v>
       </c>
       <c r="K122">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
@@ -10218,7 +10218,7 @@
         <v>20018</v>
       </c>
       <c r="K219">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="220">
